--- a/incident_report_forms/042_customs_breach_incident_form--incident_report_forms.xlsx
+++ b/incident_report_forms/042_customs_breach_incident_form--incident_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -914,12 +914,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'human_error'}</t>
+          <t>human_error</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Human Error'}</t>
+          <t>Human Error</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'system_failure'}</t>
+          <t>system_failure</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'System Failure'}</t>
+          <t>System Failure</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'system_incident'}</t>
+          <t>system_incident</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'System Incident'}</t>
+          <t>System Incident</t>
         </is>
       </c>
     </row>
@@ -1066,29 +1066,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'non_system_incident'}</t>
+          <t>non_system_incident</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Non System Incident'}</t>
+          <t>Non System Incident</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>incident_type_choices</t>
+          <t>priority_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'non_system_incident'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Non System Incident'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'low'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Low'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1117,29 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>priority_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'high'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
